--- a/Test_Cases_core_views.xlsx
+++ b/Test_Cases_core_views.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ineess_Training\bulk\Tool_Task\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0883A7E0-CE49-46BE-9FFA-DADDA991C53F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0926AC31-B228-469D-A29E-6369926A5528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="503">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -450,65 +450,6 @@
     <t>Products matching name containing 'Sugar' OR starting with 'S' are displayed</t>
   </si>
   <si>
-    <t>TC_022</t>
-  </si>
-  <si>
-    <t>Verify dashboard filter by cost price threshold &lt; 500</t>
-  </si>
-  <si>
-    <t>User has products with cost_price values above and below 500</t>
-  </si>
-  <si>
-    <t>1. Go to dashboard
-2. Enter cost_price=400
-3. Submit</t>
-  </si>
-  <si>
-    <t>cost_price=400</t>
-  </si>
-  <si>
-    <t>Only products with cost_price &lt; 500 are displayed</t>
-  </si>
-  <si>
-    <t>TC_023</t>
-  </si>
-  <si>
-    <t>Verify dashboard filter by cost price threshold between 500-999</t>
-  </si>
-  <si>
-    <t>User has products with varying cost prices</t>
-  </si>
-  <si>
-    <t>1. Go to dashboard
-2. Enter cost_price=700
-3. Submit</t>
-  </si>
-  <si>
-    <t>cost_price=700</t>
-  </si>
-  <si>
-    <t>Only products with cost_price &lt; 1000 are displayed</t>
-  </si>
-  <si>
-    <t>TC_024</t>
-  </si>
-  <si>
-    <t>Verify dashboard filter ignores non-numeric cost price input</t>
-  </si>
-  <si>
-    <t>User is on dashboard</t>
-  </si>
-  <si>
-    <t>1. Enter non-numeric value in cost_price filter (e.g. 'abc')
-2. Submit</t>
-  </si>
-  <si>
-    <t>cost_price=abc</t>
-  </si>
-  <si>
-    <t>Cost price filter is ignored (isdigit() check fails); product list unaffected by this filter</t>
-  </si>
-  <si>
     <t>TC_025</t>
   </si>
   <si>
@@ -920,13 +861,1132 @@
   </si>
   <si>
     <t>pass</t>
+  </si>
+  <si>
+    <t>not_pass</t>
+  </si>
+  <si>
+    <t>failed</t>
+  </si>
+  <si>
+    <t>TC-001</t>
+  </si>
+  <si>
+    <t>Email Service</t>
+  </si>
+  <si>
+    <t>Send email with valid email type in production</t>
+  </si>
+  <si>
+    <t>settings.SERVER_TYPE = settings.PRODUCTION</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Call </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>send_email()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> with valid type and recipient</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>email_type="signup"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>to="user@example.com"</t>
+    </r>
+  </si>
+  <si>
+    <t>Email is sent to the given recipient list</t>
+  </si>
+  <si>
+    <t>TC-002</t>
+  </si>
+  <si>
+    <t>Send email with valid email type in development</t>
+  </si>
+  <si>
+    <r>
+      <t>settings.SERVER_TYPE != settings.PRODUCTION</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>TEST_EMAIL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> configured</t>
+    </r>
+  </si>
+  <si>
+    <t>to="user@example.com"</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Email is redirected to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>settings.TEST_EMAIL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> only</t>
+    </r>
+  </si>
+  <si>
+    <t>TC-003</t>
+  </si>
+  <si>
+    <t>Reject unknown email type</t>
+  </si>
+  <si>
+    <t>Application is running</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Call </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>send_email()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> with invalid type</t>
+    </r>
+  </si>
+  <si>
+    <t>email_type="abc"</t>
+  </si>
+  <si>
+    <t>ValueError is raised with valid email types message</t>
+  </si>
+  <si>
+    <t>TC-004</t>
+  </si>
+  <si>
+    <t>Send email with string recipient</t>
+  </si>
+  <si>
+    <t>Valid email builder exists</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Call </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>send_email()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> with </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>to</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> as a string</t>
+    </r>
+  </si>
+  <si>
+    <t>Recipient is converted into a list and task is called</t>
+  </si>
+  <si>
+    <t>TC-005</t>
+  </si>
+  <si>
+    <t>Send email with multiple recipients</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Call </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>send_email()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> with list of recipients</t>
+    </r>
+  </si>
+  <si>
+    <t>to=["a@example.com", "b@example.com"]</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">All recipients are passed to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>deliver_email</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> in production</t>
+    </r>
+  </si>
+  <si>
+    <t>TC-006</t>
+  </si>
+  <si>
+    <t>Send email with CC list</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Call </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>send_email()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> with </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>cc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> values</t>
+    </r>
+  </si>
+  <si>
+    <t>cc="cc@example.com"</t>
+  </si>
+  <si>
+    <t>CC is converted to list and passed in production</t>
+  </si>
+  <si>
+    <t>TC-007</t>
+  </si>
+  <si>
+    <t>Send email with empty context</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Call </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>send_email()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> without context</t>
+    </r>
+  </si>
+  <si>
+    <t>context=None</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Empty dict is passed to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>deliver_email</t>
+    </r>
+  </si>
+  <si>
+    <t>TC-008</t>
+  </si>
+  <si>
+    <t>Confirm development mode does not send to real user</t>
+  </si>
+  <si>
+    <r>
+      <t>SERVER_TYPE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> set to non-production</t>
+    </r>
+  </si>
+  <si>
+    <t>Call signup or notification flow</t>
+  </si>
+  <si>
+    <t>Real user email present</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Email is sent only to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>TEST_EMAIL</t>
+    </r>
+  </si>
+  <si>
+    <t>TC-009</t>
+  </si>
+  <si>
+    <t>Confirm production mode sends to actual recipient</t>
+  </si>
+  <si>
+    <t>SERVER_TYPE = PRODUCTION</t>
+  </si>
+  <si>
+    <t>Trigger signup or error email</t>
+  </si>
+  <si>
+    <t>Email goes to actual recipient</t>
+  </si>
+  <si>
+    <t>TC-010</t>
+  </si>
+  <si>
+    <t>Verify task receives user_id</t>
+  </si>
+  <si>
+    <t>Email builder supports user_id</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Call </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>send_email()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> with </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>user_id</t>
+    </r>
+  </si>
+  <si>
+    <t>user_id=1</t>
+  </si>
+  <si>
+    <r>
+      <t>deliver_email</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> receives correct </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>user_id</t>
+    </r>
+  </si>
+  <si>
+    <t>Template Validation</t>
+  </si>
+  <si>
+    <t>Upload file with correct column order</t>
+  </si>
+  <si>
+    <t>Open upload page, select valid template file, click upload</t>
+  </si>
+  <si>
+    <t>Valid CSV/XLSX with exact columns</t>
+  </si>
+  <si>
+    <t>File is accepted and rows are processed</t>
+  </si>
+  <si>
+    <t>Upload file with missing column</t>
+  </si>
+  <si>
+    <t>Upload file missing one required header</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Missing </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Quantity*</t>
+    </r>
+  </si>
+  <si>
+    <t>Template error is shown mentioning missing column</t>
+  </si>
+  <si>
+    <t>Upload file with extra column</t>
+  </si>
+  <si>
+    <t>Upload file with an additional unwanted column</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Extra </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Brand</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> column</t>
+    </r>
+  </si>
+  <si>
+    <t>Template error is shown mentioning unexpected extra column</t>
+  </si>
+  <si>
+    <t>Upload file with wrong column order</t>
+  </si>
+  <si>
+    <t>Upload file with same columns but different order</t>
+  </si>
+  <si>
+    <t>Columns shuffled</t>
+  </si>
+  <si>
+    <t>Error shown for column order mismatch</t>
+  </si>
+  <si>
+    <t>Product Code Validation</t>
+  </si>
+  <si>
+    <t>Upload valid product code</t>
+  </si>
+  <si>
+    <t>Upload row with valid product code</t>
+  </si>
+  <si>
+    <t>P1001</t>
+  </si>
+  <si>
+    <t>Row passes validation</t>
+  </si>
+  <si>
+    <t>Upload missing product code</t>
+  </si>
+  <si>
+    <t>Upload row with empty product code</t>
+  </si>
+  <si>
+    <t>Blank</t>
+  </si>
+  <si>
+    <t>Error: Product Code is required</t>
+  </si>
+  <si>
+    <t>Upload invalid product code format</t>
+  </si>
+  <si>
+    <t>Upload row with wrong code pattern</t>
+  </si>
+  <si>
+    <r>
+      <t>1001</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> or </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>PX01</t>
+    </r>
+  </si>
+  <si>
+    <t>Error: Product Code must start with P and have 4 or more digits</t>
+  </si>
+  <si>
+    <t>Upload duplicate product code in file</t>
+  </si>
+  <si>
+    <t>Upload file with same product code twice</t>
+  </si>
+  <si>
+    <r>
+      <t>P1001</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> repeated</t>
+    </r>
+  </si>
+  <si>
+    <t>Error: Duplicate Product Code within uploaded file</t>
+  </si>
+  <si>
+    <t>Upload existing product code</t>
+  </si>
+  <si>
+    <t>Product already exists in DB</t>
+  </si>
+  <si>
+    <t>Upload row with existing product code</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Existing </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>P1001</t>
+    </r>
+  </si>
+  <si>
+    <t>Error: Product Code already exists in database</t>
+  </si>
+  <si>
+    <t>Product Name Validation</t>
+  </si>
+  <si>
+    <t>Upload valid product name</t>
+  </si>
+  <si>
+    <t>Upload row with valid product name</t>
+  </si>
+  <si>
+    <t>Milk Powder</t>
+  </si>
+  <si>
+    <t>TC-011</t>
+  </si>
+  <si>
+    <t>Upload missing product name</t>
+  </si>
+  <si>
+    <t>Upload row with blank product name</t>
+  </si>
+  <si>
+    <t>Error: Product Name is required</t>
+  </si>
+  <si>
+    <t>TC-012</t>
+  </si>
+  <si>
+    <t>Upload product name exceeding length</t>
+  </si>
+  <si>
+    <t>Upload row with long product name</t>
+  </si>
+  <si>
+    <t>More than 50 characters</t>
+  </si>
+  <si>
+    <t>Error: Product Name must below 50 characters</t>
+  </si>
+  <si>
+    <t>TC-013</t>
+  </si>
+  <si>
+    <t>Upload invalid product name characters</t>
+  </si>
+  <si>
+    <t>Upload row with special characters</t>
+  </si>
+  <si>
+    <t>@Milk#123</t>
+  </si>
+  <si>
+    <t>Error: Product Name must contain only letters</t>
+  </si>
+  <si>
+    <t>TC-014</t>
+  </si>
+  <si>
+    <t>Upload duplicate product name in file</t>
+  </si>
+  <si>
+    <t>Upload file with same name twice</t>
+  </si>
+  <si>
+    <r>
+      <t>Milk Powder</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> repeated</t>
+    </r>
+  </si>
+  <si>
+    <t>Error: Duplicate Product Name within uploaded file</t>
+  </si>
+  <si>
+    <t>TC-015</t>
+  </si>
+  <si>
+    <t>Upload existing product name</t>
+  </si>
+  <si>
+    <t>Upload row with existing product name</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Existing </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Milk Powder</t>
+    </r>
+  </si>
+  <si>
+    <t>Error: Product Name already exists in database</t>
+  </si>
+  <si>
+    <t>TC-016</t>
+  </si>
+  <si>
+    <t>Description Validation</t>
+  </si>
+  <si>
+    <t>Upload description within limit</t>
+  </si>
+  <si>
+    <t>Upload valid description</t>
+  </si>
+  <si>
+    <t>Short description</t>
+  </si>
+  <si>
+    <t>TC-017</t>
+  </si>
+  <si>
+    <t>Upload description exceeding limit</t>
+  </si>
+  <si>
+    <t>Upload row with long description</t>
+  </si>
+  <si>
+    <t>More than 150 characters</t>
+  </si>
+  <si>
+    <t>Error: Description must be at most 150 characters</t>
+  </si>
+  <si>
+    <t>TC-018</t>
+  </si>
+  <si>
+    <t>Category Validation</t>
+  </si>
+  <si>
+    <t>Upload valid category</t>
+  </si>
+  <si>
+    <t>Upload valid item category</t>
+  </si>
+  <si>
+    <t>Dairy</t>
+  </si>
+  <si>
+    <t>TC-019</t>
+  </si>
+  <si>
+    <t>Upload category exceeding limit</t>
+  </si>
+  <si>
+    <t>Upload long category value</t>
+  </si>
+  <si>
+    <t>Error: Item Category must be at most 50 characters</t>
+  </si>
+  <si>
+    <t>TC-020</t>
+  </si>
+  <si>
+    <t>Quantity Validation</t>
+  </si>
+  <si>
+    <t>Upload valid quantity</t>
+  </si>
+  <si>
+    <t>Upload row with valid quantity</t>
+  </si>
+  <si>
+    <t>TC-021</t>
+  </si>
+  <si>
+    <t>Upload missing quantity</t>
+  </si>
+  <si>
+    <t>Upload row with blank quantity</t>
+  </si>
+  <si>
+    <t>Error: Quantity is required</t>
+  </si>
+  <si>
+    <t>TC-022</t>
+  </si>
+  <si>
+    <t>Upload negative quantity</t>
+  </si>
+  <si>
+    <t>Upload row with negative quantity</t>
+  </si>
+  <si>
+    <t>Error: Quantity must be greater than or equal to 0</t>
+  </si>
+  <si>
+    <t>TC-023</t>
+  </si>
+  <si>
+    <t>Upload quantity above limit</t>
+  </si>
+  <si>
+    <t>Upload row with quantity above max</t>
+  </si>
+  <si>
+    <t>Error: Quantity must not exceed 5000</t>
+  </si>
+  <si>
+    <t>TC-024</t>
+  </si>
+  <si>
+    <t>Upload quantity with decimal</t>
+  </si>
+  <si>
+    <t>Upload row with decimal quantity</t>
+  </si>
+  <si>
+    <t>Error: Quantity must be a whole integer</t>
+  </si>
+  <si>
+    <t>TC-025</t>
+  </si>
+  <si>
+    <t>Selling Price Validation</t>
+  </si>
+  <si>
+    <t>Upload valid selling price</t>
+  </si>
+  <si>
+    <t>Upload row with valid price</t>
+  </si>
+  <si>
+    <t>TC-026</t>
+  </si>
+  <si>
+    <t>Upload missing selling price</t>
+  </si>
+  <si>
+    <t>Upload row with blank selling price</t>
+  </si>
+  <si>
+    <t>Error: Selling Price is required</t>
+  </si>
+  <si>
+    <t>TC-027</t>
+  </si>
+  <si>
+    <t>Upload invalid selling price format</t>
+  </si>
+  <si>
+    <t>Upload row with text in price field</t>
+  </si>
+  <si>
+    <t>abc</t>
+  </si>
+  <si>
+    <t>Error: Selling Price must be a valid decimal number</t>
+  </si>
+  <si>
+    <t>TC-028</t>
+  </si>
+  <si>
+    <t>Upload negative selling price</t>
+  </si>
+  <si>
+    <t>Upload row with negative price</t>
+  </si>
+  <si>
+    <t>Error: Selling Price must be greater than or equal to 0</t>
+  </si>
+  <si>
+    <t>TC-029</t>
+  </si>
+  <si>
+    <t>Cost Price Validation</t>
+  </si>
+  <si>
+    <t>Upload valid cost price</t>
+  </si>
+  <si>
+    <t>Upload row with valid cost price</t>
+  </si>
+  <si>
+    <t>TC-030</t>
+  </si>
+  <si>
+    <t>Upload invalid cost price format</t>
+  </si>
+  <si>
+    <t>Upload row with text in cost price</t>
+  </si>
+  <si>
+    <t>xyz</t>
+  </si>
+  <si>
+    <t>Error: Cost Price must be a valid decimal number</t>
+  </si>
+  <si>
+    <t>TC-031</t>
+  </si>
+  <si>
+    <t>Upload negative cost price</t>
+  </si>
+  <si>
+    <t>Upload row with negative value</t>
+  </si>
+  <si>
+    <t>Error: Cost Price must be greater than or equal to 0</t>
+  </si>
+  <si>
+    <t>TC-032</t>
+  </si>
+  <si>
+    <t>Upload cost price above limit</t>
+  </si>
+  <si>
+    <t>Upload row with large cost price</t>
+  </si>
+  <si>
+    <t>Error: Cost Price must not exceed ₹1,00,00,000</t>
+  </si>
+  <si>
+    <t>TC-033</t>
+  </si>
+  <si>
+    <t>Expire Date Validation</t>
+  </si>
+  <si>
+    <t>Upload valid future date</t>
+  </si>
+  <si>
+    <t>Upload row with future date</t>
+  </si>
+  <si>
+    <t>TC-034</t>
+  </si>
+  <si>
+    <t>Upload invalid date format</t>
+  </si>
+  <si>
+    <t>Upload row with wrong date format</t>
+  </si>
+  <si>
+    <t>Error: Expire Date must be in YYYY-MM-DD format</t>
+  </si>
+  <si>
+    <t>TC-035</t>
+  </si>
+  <si>
+    <t>Upload past expiry date</t>
+  </si>
+  <si>
+    <t>Upload row with old date</t>
+  </si>
+  <si>
+    <t>Error: Expire Date must not be in the past</t>
+  </si>
+  <si>
+    <t>TC-036</t>
+  </si>
+  <si>
+    <t>Upload Processing</t>
+  </si>
+  <si>
+    <t>Upload file with all valid rows</t>
+  </si>
+  <si>
+    <t>Upload complete valid file</t>
+  </si>
+  <si>
+    <t>Valid CSV/XLSX</t>
+  </si>
+  <si>
+    <t>All rows inserted successfully</t>
+  </si>
+  <si>
+    <t>TC-037</t>
+  </si>
+  <si>
+    <t>Upload file with mixed valid and invalid rows</t>
+  </si>
+  <si>
+    <t>Upload file containing both types</t>
+  </si>
+  <si>
+    <t>Mixed data</t>
+  </si>
+  <si>
+    <t>Valid rows inserted, invalid rows saved separately</t>
+  </si>
+  <si>
+    <t>TC-038</t>
+  </si>
+  <si>
+    <t>Upload unsupported file type</t>
+  </si>
+  <si>
+    <t>Upload non-CSV/XLSX file</t>
+  </si>
+  <si>
+    <r>
+      <t>.txt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> file</t>
+    </r>
+  </si>
+  <si>
+    <t>Upload rejected or no processing done</t>
+  </si>
+  <si>
+    <t>TC-039</t>
+  </si>
+  <si>
+    <t>Invalid Rows Report</t>
+  </si>
+  <si>
+    <t>View invalid rows after upload failure</t>
+  </si>
+  <si>
+    <t>Invalid rows exist</t>
+  </si>
+  <si>
+    <t>Open invalid rows page</t>
+  </si>
+  <si>
+    <t>Invalid rows are displayed with error details</t>
+  </si>
+  <si>
+    <t>TC-040</t>
+  </si>
+  <si>
+    <t>Invalid Rows Download</t>
+  </si>
+  <si>
+    <t>Download invalid rows Excel</t>
+  </si>
+  <si>
+    <t>Click download invalid data</t>
+  </si>
+  <si>
+    <t>Excel file downloads with invalid rows data</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -940,8 +2000,26 @@
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -960,8 +2038,14 @@
         <bgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -984,11 +2068,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDDDDDD"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDDDDDD"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFDDDDDD"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFDDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -998,6 +2097,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1301,8 +2412,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I104"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -1315,7 +2426,7 @@
     <col min="9" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1344,7 +2455,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="28.8">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -1367,13 +2478,13 @@
         <v>15</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="57.6">
       <c r="A3" s="2" t="s">
         <v>16</v>
       </c>
@@ -1396,13 +2507,13 @@
         <v>21</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="28.8">
       <c r="A4" s="2" t="s">
         <v>22</v>
       </c>
@@ -1425,13 +2536,13 @@
         <v>27</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="43.2">
       <c r="A5" s="2" t="s">
         <v>28</v>
       </c>
@@ -1454,13 +2565,13 @@
         <v>33</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="43.2">
       <c r="A6" s="2" t="s">
         <v>34</v>
       </c>
@@ -1483,13 +2594,13 @@
         <v>40</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="43.2">
       <c r="A7" s="2" t="s">
         <v>41</v>
       </c>
@@ -1512,13 +2623,13 @@
         <v>46</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="43.2">
       <c r="A8" s="2" t="s">
         <v>47</v>
       </c>
@@ -1541,13 +2652,13 @@
         <v>52</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="43.2">
       <c r="A9" s="2" t="s">
         <v>53</v>
       </c>
@@ -1570,13 +2681,13 @@
         <v>57</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="57.6">
       <c r="A10" s="2" t="s">
         <v>58</v>
       </c>
@@ -1599,13 +2710,13 @@
         <v>63</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="43.2">
       <c r="A11" s="2" t="s">
         <v>64</v>
       </c>
@@ -1628,13 +2739,13 @@
         <v>70</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="43.2">
       <c r="A12" s="2" t="s">
         <v>71</v>
       </c>
@@ -1657,13 +2768,13 @@
         <v>76</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="43.2">
       <c r="A13" s="2" t="s">
         <v>77</v>
       </c>
@@ -1686,13 +2797,13 @@
         <v>82</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="43.2">
       <c r="A14" s="2" t="s">
         <v>83</v>
       </c>
@@ -1715,13 +2826,13 @@
         <v>88</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="43.2">
       <c r="A15" s="2" t="s">
         <v>89</v>
       </c>
@@ -1744,13 +2855,13 @@
         <v>94</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="43.2">
       <c r="A16" s="2" t="s">
         <v>95</v>
       </c>
@@ -1773,13 +2884,13 @@
         <v>100</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="43.2">
       <c r="A17" s="2" t="s">
         <v>101</v>
       </c>
@@ -1802,13 +2913,13 @@
         <v>106</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="28.8">
       <c r="A18" s="2" t="s">
         <v>107</v>
       </c>
@@ -1831,13 +2942,13 @@
         <v>112</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="28.8">
       <c r="A19" s="2" t="s">
         <v>113</v>
       </c>
@@ -1860,13 +2971,13 @@
         <v>116</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="28.8">
       <c r="A20" s="2" t="s">
         <v>117</v>
       </c>
@@ -1889,13 +3000,13 @@
         <v>122</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="43.2">
       <c r="A21" s="2" t="s">
         <v>123</v>
       </c>
@@ -1918,13 +3029,13 @@
         <v>128</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="43.2">
       <c r="A22" s="2" t="s">
         <v>129</v>
       </c>
@@ -1947,794 +3058,2032 @@
         <v>134</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="3"/>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="3"/>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="3"/>
+    </row>
+    <row r="26" spans="1:9" ht="28.8">
+      <c r="A26" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>118</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="28.8">
       <c r="A27" s="2" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>118</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="43.2">
       <c r="A28" s="2" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="43.2">
       <c r="A29" s="2" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="28.8">
       <c r="A30" s="2" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="28.8">
       <c r="A31" s="2" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>182</v>
-      </c>
       <c r="D31" s="2" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="43.2">
       <c r="A32" s="2" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="43.2">
       <c r="A33" s="2" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="43.2">
       <c r="A34" s="2" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="28.8">
       <c r="A35" s="2" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>110</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="43.2">
       <c r="A36" s="2" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="28.8">
       <c r="A37" s="2" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>110</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="57.6">
       <c r="A38" s="2" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>110</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="43.2">
       <c r="A39" s="2" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>110</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="43.2">
       <c r="A40" s="2" t="s">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="28.8">
       <c r="A41" s="2" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="43.2">
       <c r="A42" s="2" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="28.8">
       <c r="A43" s="2" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="28.8">
       <c r="A44" s="2" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="43.2">
       <c r="A45" s="2" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="28.8">
       <c r="A46" s="2" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>91</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G46" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="I46" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="H46" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:9" ht="28.8">
       <c r="A47" s="2" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="28.8">
       <c r="A48" s="2" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="28.8">
       <c r="A49" s="2" t="s">
-        <v>278</v>
+        <v>260</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G49" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="15" thickBot="1"/>
+    <row r="52" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A52" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A53" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
+    </row>
+    <row r="54" spans="1:9" ht="41.4" thickBot="1">
+      <c r="A54" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="H54" s="5"/>
+      <c r="I54" s="5"/>
+    </row>
+    <row r="55" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A55" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="C55" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="H49" s="2" t="s">
+      <c r="D55" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="I49" s="3" t="s">
+      <c r="E55" s="5" t="s">
         <v>284</v>
       </c>
+      <c r="F55" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="H55" s="5"/>
+      <c r="I55" s="5"/>
+    </row>
+    <row r="56" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A56" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="H56" s="5"/>
+      <c r="I56" s="5"/>
+    </row>
+    <row r="57" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A57" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="H57" s="5"/>
+      <c r="I57" s="5"/>
+    </row>
+    <row r="58" spans="1:9" ht="15" thickBot="1">
+      <c r="A58" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="H58" s="5"/>
+      <c r="I58" s="5"/>
+    </row>
+    <row r="59" spans="1:9" ht="15" thickBot="1">
+      <c r="A59" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="H59" s="5"/>
+      <c r="I59" s="5"/>
+    </row>
+    <row r="60" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A60" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="H60" s="5"/>
+      <c r="I60" s="5"/>
+    </row>
+    <row r="61" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A61" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="H61" s="5"/>
+      <c r="I61" s="5"/>
+    </row>
+    <row r="62" spans="1:9" ht="15" thickBot="1">
+      <c r="A62" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="H62" s="5"/>
+      <c r="I62" s="5"/>
+    </row>
+    <row r="63" spans="1:9" ht="15" thickBot="1"/>
+    <row r="64" spans="1:9" ht="15" thickBot="1">
+      <c r="A64" s="4"/>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+    </row>
+    <row r="65" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A65" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="H65" s="5"/>
+      <c r="I65" s="5"/>
+    </row>
+    <row r="66" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A66" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="H66" s="5"/>
+      <c r="I66" s="5"/>
+    </row>
+    <row r="67" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A67" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="H67" s="5"/>
+      <c r="I67" s="5"/>
+    </row>
+    <row r="68" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A68" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5"/>
+    </row>
+    <row r="69" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A69" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="F69" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="H69" s="5"/>
+      <c r="I69" s="5"/>
+    </row>
+    <row r="70" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A70" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="H70" s="5"/>
+      <c r="I70" s="5"/>
+    </row>
+    <row r="71" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A71" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="F71" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="H71" s="5"/>
+      <c r="I71" s="5"/>
+    </row>
+    <row r="72" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A72" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="H72" s="5"/>
+      <c r="I72" s="5"/>
+    </row>
+    <row r="73" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A73" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="H73" s="5"/>
+      <c r="I73" s="5"/>
+    </row>
+    <row r="74" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A74" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="G74" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="H74" s="5"/>
+      <c r="I74" s="5"/>
+    </row>
+    <row r="75" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A75" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="G75" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="H75" s="5"/>
+      <c r="I75" s="5"/>
+    </row>
+    <row r="76" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A76" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="F76" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="H76" s="5"/>
+      <c r="I76" s="5"/>
+    </row>
+    <row r="77" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A77" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="F77" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="G77" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="H77" s="5"/>
+      <c r="I77" s="5"/>
+    </row>
+    <row r="78" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A78" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="H78" s="5"/>
+      <c r="I78" s="5"/>
+    </row>
+    <row r="79" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A79" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="F79" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="G79" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="H79" s="5"/>
+      <c r="I79" s="5"/>
+    </row>
+    <row r="80" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A80" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="F80" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="G80" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="H80" s="5"/>
+      <c r="I80" s="5"/>
+    </row>
+    <row r="81" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A81" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E81" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="F81" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="G81" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="H81" s="5"/>
+      <c r="I81" s="5"/>
+    </row>
+    <row r="82" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A82" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="F82" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="G82" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="H82" s="5"/>
+      <c r="I82" s="5"/>
+    </row>
+    <row r="83" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A83" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="F83" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="G83" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="H83" s="5"/>
+      <c r="I83" s="5"/>
+    </row>
+    <row r="84" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A84" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="F84" s="6">
+        <v>10</v>
+      </c>
+      <c r="G84" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="H84" s="5"/>
+      <c r="I84" s="5"/>
+    </row>
+    <row r="85" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A85" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="F85" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="G85" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="H85" s="5"/>
+      <c r="I85" s="5"/>
+    </row>
+    <row r="86" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A86" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="F86" s="6">
+        <v>-5</v>
+      </c>
+      <c r="G86" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="H86" s="5"/>
+      <c r="I86" s="5"/>
+    </row>
+    <row r="87" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A87" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="F87" s="6">
+        <v>5001</v>
+      </c>
+      <c r="G87" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="H87" s="5"/>
+      <c r="I87" s="5"/>
+    </row>
+    <row r="88" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A88" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="F88" s="6">
+        <v>10.5</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="H88" s="5"/>
+      <c r="I88" s="5"/>
+    </row>
+    <row r="89" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A89" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="F89" s="6">
+        <v>120.5</v>
+      </c>
+      <c r="G89" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="H89" s="5"/>
+      <c r="I89" s="5"/>
+    </row>
+    <row r="90" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A90" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="G90" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="H90" s="5"/>
+      <c r="I90" s="5"/>
+    </row>
+    <row r="91" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A91" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E91" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="F91" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="H91" s="5"/>
+      <c r="I91" s="5"/>
+    </row>
+    <row r="92" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A92" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E92" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="F92" s="6">
+        <v>-10</v>
+      </c>
+      <c r="G92" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="H92" s="5"/>
+      <c r="I92" s="5"/>
+    </row>
+    <row r="93" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A93" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="F93" s="6">
+        <v>100</v>
+      </c>
+      <c r="G93" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="H93" s="5"/>
+      <c r="I93" s="5"/>
+    </row>
+    <row r="94" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A94" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E94" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="H94" s="5"/>
+      <c r="I94" s="5"/>
+    </row>
+    <row r="95" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A95" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E95" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="F95" s="6">
+        <v>-50</v>
+      </c>
+      <c r="G95" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="H95" s="5"/>
+      <c r="I95" s="5"/>
+    </row>
+    <row r="96" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A96" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E96" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="F96" s="6">
+        <v>10000001</v>
+      </c>
+      <c r="G96" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="H96" s="5"/>
+      <c r="I96" s="5"/>
+    </row>
+    <row r="97" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A97" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="F97" s="7">
+        <v>46387</v>
+      </c>
+      <c r="G97" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="H97" s="5"/>
+      <c r="I97" s="5"/>
+    </row>
+    <row r="98" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A98" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="F98" s="7">
+        <v>46387</v>
+      </c>
+      <c r="G98" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="H98" s="5"/>
+      <c r="I98" s="5"/>
+    </row>
+    <row r="99" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A99" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E99" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="F99" s="7">
+        <v>45292</v>
+      </c>
+      <c r="G99" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="H99" s="5"/>
+      <c r="I99" s="5"/>
+    </row>
+    <row r="100" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A100" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="D100" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E100" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="F100" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="G100" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="H100" s="5"/>
+      <c r="I100" s="5"/>
+    </row>
+    <row r="101" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A101" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="D101" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E101" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="F101" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="G101" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="H101" s="5"/>
+      <c r="I101" s="5"/>
+    </row>
+    <row r="102" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A102" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="D102" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E102" s="5" t="s">
+        <v>489</v>
+      </c>
+      <c r="F102" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="G102" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="H102" s="5"/>
+      <c r="I102" s="5"/>
+    </row>
+    <row r="103" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A103" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>494</v>
+      </c>
+      <c r="D103" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="E103" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="F103" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G103" s="5" t="s">
+        <v>497</v>
+      </c>
+      <c r="H103" s="5"/>
+      <c r="I103" s="5"/>
+    </row>
+    <row r="104" spans="1:9" ht="28.2" thickBot="1">
+      <c r="A104" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="D104" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="E104" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="F104" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G104" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="H104" s="5"/>
+      <c r="I104" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
